--- a/output/pdf_financials_xlsx/TGC.xlsx
+++ b/output/pdf_financials_xlsx/TGC.xlsx
@@ -2798,19 +2798,19 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.095531</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.095531</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.095531</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.095531</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.717675</v>
       </c>
     </row>
     <row r="93">
@@ -4488,7 +4488,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -4866,7 +4870,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TGC.xlsx
+++ b/output/pdf_financials_xlsx/TGC.xlsx
@@ -1289,16 +1289,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.106708</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.460799</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.384668</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.309723</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>0.101499</v>
@@ -1339,16 +1339,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.106708</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.460799</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.384668</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.309723</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>0.101499</v>
@@ -4660,7 +4660,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E17" s="5" t="n">

--- a/output/pdf_financials_xlsx/TGC.xlsx
+++ b/output/pdf_financials_xlsx/TGC.xlsx
@@ -574,16 +574,16 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.00525</v>
+        <v>0.005292</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.028925</v>
+        <v>0.032457</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.013808</v>
+        <v>0.017937</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.016899</v>
+        <v>0.018719</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0.03785</v>
@@ -649,16 +649,16 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.00525</v>
+        <v>0.005292</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.028925</v>
+        <v>0.032457</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.013808</v>
+        <v>0.017937</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.016899</v>
+        <v>0.018719</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>0.217053</v>
@@ -674,16 +674,16 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.00525</v>
+        <v>-0.005292</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.028925</v>
+        <v>-0.032457</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.013808</v>
+        <v>-0.017937</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.016899</v>
+        <v>-0.018719</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>-0.217053</v>
@@ -3011,13 +3011,13 @@
         <v>0</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>-0.008218</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0</v>
+        <v>-0.169419</v>
       </c>
     </row>
     <row r="102">
@@ -3136,13 +3136,13 @@
         <v>-0.006424</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.008521000000000001</v>
+        <v>0.008522</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0.05787</v>
+        <v>0.049652</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>-0.173607</v>
+        <v>-0.343026</v>
       </c>
     </row>
     <row r="107">
@@ -5152,7 +5152,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -6286,7 +6290,11 @@
           <t>Prepaid expenses and GST receivable</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -9412,7 +9420,11 @@
           <t>Office expense</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E121" s="5" t="n">
         <v>4.2e-05</v>
       </c>
